--- a/data/trans_dic/P56$pareja-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 73,13</t>
+          <t>17,22; 72,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,21; 85,52</t>
+          <t>44,66; 85,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,33; 90,44</t>
+          <t>46,14; 90,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 69,27</t>
+          <t>43,24; 71,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 60,15</t>
+          <t>18,6; 56,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,65; 42,31</t>
+          <t>13,9; 42,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,49; 44,19</t>
+          <t>16,33; 42,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,47; 44,93</t>
+          <t>25,79; 44,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 57,84</t>
+          <t>25,95; 57,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,48; 55,09</t>
+          <t>28,41; 52,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,33; 57,61</t>
+          <t>30,78; 56,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,42; 50,47</t>
+          <t>33,71; 50,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 57,58</t>
+          <t>24,9; 56,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,28; 50,23</t>
+          <t>21,05; 49,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,55; 50,52</t>
+          <t>24,22; 51,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 35,74</t>
+          <t>21,32; 38,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,31</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,39</t>
+          <t>7,38; 17,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 17,09</t>
+          <t>4,4; 18,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,12</t>
+          <t>7,02; 12,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 23,27</t>
+          <t>10,15; 22,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 23,73</t>
+          <t>12,26; 23,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,04; 22,97</t>
+          <t>12,06; 23,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 17,6</t>
+          <t>11,63; 18,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 57,02</t>
+          <t>27,88; 54,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,0</t>
+          <t>30,44; 55,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 57,32</t>
+          <t>37,16; 59,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,15; 43,81</t>
+          <t>29,36; 44,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,18</t>
+          <t>6,24; 20,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 20,71</t>
+          <t>9,99; 20,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,65</t>
+          <t>8,91; 20,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,35</t>
+          <t>11,92; 18,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 28,97</t>
+          <t>16,13; 29,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,62; 28,11</t>
+          <t>16,66; 27,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,7</t>
+          <t>18,48; 29,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,11</t>
+          <t>18,01; 24,42</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>38213</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2559; 9408</t>
+          <t>2216; 9379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9688; 18325</t>
+          <t>9571; 18335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10197; 19081</t>
+          <t>9734; 19060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12468; 20540</t>
+          <t>13395; 22305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4334; 13275</t>
+          <t>4105; 12521</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5751; 17827</t>
+          <t>5855; 17829</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6792; 18198</t>
+          <t>6725; 17323</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14031; 23812</t>
+          <t>15337; 26317</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9110; 20205</t>
+          <t>9064; 20086</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18102; 35017</t>
+          <t>18058; 33621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20134; 35881</t>
+          <t>19168; 35095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29278; 41716</t>
+          <t>30485; 45443</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>42870</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9214; 20391</t>
+          <t>8817; 20101</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12148; 28666</t>
+          <t>12014; 28023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12522; 25765</t>
+          <t>12352; 26232</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14340; 25875</t>
+          <t>16546; 29507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 9515</t>
+          <t>0; 8693</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11842; 28364</t>
+          <t>12037; 28575</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5714; 22316</t>
+          <t>5749; 23637</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13349; 24003</t>
+          <t>15166; 28016</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9632; 24876</t>
+          <t>10845; 24439</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27384; 52254</t>
+          <t>26991; 51628</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21872; 41709</t>
+          <t>21904; 43508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31170; 47603</t>
+          <t>34152; 53385</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>81083</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14530; 27529</t>
+          <t>13462; 26214</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23659; 43177</t>
+          <t>23900; 43723</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25572; 41326</t>
+          <t>26789; 43080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29755; 44707</t>
+          <t>31882; 48288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5442; 17941</t>
+          <t>5841; 19438</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20387; 42514</t>
+          <t>20512; 41476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14730; 35472</t>
+          <t>15306; 35917</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29544; 46061</t>
+          <t>32831; 50323</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22241; 41080</t>
+          <t>22875; 42002</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49996; 79773</t>
+          <t>47261; 78376</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44807; 72443</t>
+          <t>45064; 73099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61941; 85141</t>
+          <t>69153; 93755</t>
         </is>
       </c>
     </row>
